--- a/SNGM_Capacitacion_3.8_Operaciones.xlsx
+++ b/SNGM_Capacitacion_3.8_Operaciones.xlsx
@@ -12498,7 +12498,7 @@
       </c>
       <c r="AK19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="AL19" s="22" t="inlineStr">
@@ -12508,7 +12508,7 @@
       </c>
       <c r="AM19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="AN19" s="22" t="inlineStr">
@@ -12518,7 +12518,7 @@
       </c>
       <c r="AO19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="AP19" s="22" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="AQ19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="AR19" s="22" t="inlineStr">
@@ -12538,7 +12538,7 @@
       </c>
       <c r="AS19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="AT19" s="22" t="inlineStr">
@@ -12548,7 +12548,7 @@
       </c>
       <c r="AU19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="AV19" s="22" t="inlineStr">
@@ -12558,7 +12558,7 @@
       </c>
       <c r="AW19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="AX19" s="22" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="AY19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="AZ19" s="22" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="BA19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BB19" s="22" t="inlineStr">
@@ -12588,7 +12588,7 @@
       </c>
       <c r="BC19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BD19" s="22" t="inlineStr">
@@ -12598,7 +12598,7 @@
       </c>
       <c r="BE19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BF19" s="22" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="BG19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BH19" s="22" t="inlineStr">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="BI19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ19" s="22" t="inlineStr">
@@ -12628,7 +12628,7 @@
       </c>
       <c r="BK19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BL19" s="22" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="BM19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BN19" s="22" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="BO19" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>24/09/2026 / 100%</t>
         </is>
       </c>
     </row>
@@ -14358,7 +14358,7 @@
       </c>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -14368,7 +14368,7 @@
       </c>
       <c r="I25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -14378,7 +14378,7 @@
       </c>
       <c r="K25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="M25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="N25" s="22" t="inlineStr">
@@ -14398,7 +14398,7 @@
       </c>
       <c r="O25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="P25" s="22" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="Q25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="R25" s="22" t="inlineStr">
@@ -14418,7 +14418,7 @@
       </c>
       <c r="S25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="T25" s="22" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="BA25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BB25" s="22" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="BC25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BD25" s="22" t="inlineStr">
@@ -14608,7 +14608,7 @@
       </c>
       <c r="BE25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BF25" s="22" t="inlineStr">
@@ -14618,7 +14618,7 @@
       </c>
       <c r="BG25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BH25" s="22" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="BI25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BJ25" s="22" t="inlineStr">
@@ -14638,7 +14638,7 @@
       </c>
       <c r="BK25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BL25" s="22" t="inlineStr">
@@ -14648,7 +14648,7 @@
       </c>
       <c r="BM25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
       <c r="BN25" s="22" t="inlineStr">
@@ -14658,7 +14658,7 @@
       </c>
       <c r="BO25" s="22" t="inlineStr">
         <is>
-          <t>30/08/2026 / 100%</t>
+          <t>30/09/2026 / 100%</t>
         </is>
       </c>
     </row>
